--- a/samples/sample_cskh_pipeline_output.xlsx
+++ b/samples/sample_cskh_pipeline_output.xlsx
@@ -1,129 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vngms-my.sharepoint.com/personal/vanpnh_vng_com_vn/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{8B37B779-67D8-41FA-8D16-A40587A94484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Phan hoi ZaloPay" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
-  <si>
-    <t>Issue Key</t>
-  </si>
-  <si>
-    <t>Loại vấn đề</t>
-  </si>
-  <si>
-    <t>Root Cause</t>
-  </si>
-  <si>
-    <t>SLA Status</t>
-  </si>
-  <si>
-    <t>Escalate đến</t>
-  </si>
-  <si>
-    <t>Phản hồi ZaloPay</t>
-  </si>
-  <si>
-    <t>Trạng thái</t>
-  </si>
-  <si>
-    <t>ISSUE-40991</t>
-  </si>
-  <si>
-    <t>Account_ChangeInfo</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>ISSUE-40967</t>
-  </si>
-  <si>
-    <t>Promotion campaign</t>
-  </si>
-  <si>
-    <t>Team Cấu hình Khuyến mãi</t>
-  </si>
-  <si>
-    <t>Chào bạn,
-Zalopay xin lỗi vì đã để bạn có những trải nghiệm không tốt khi sử dụng dịch vụ.
-Về yêu cầu xác nhận lỗi cấu hình chương trình khuyến mãi 2748 mà bạn gửi đến, Zalopay xin phép báo cáo tình hình xử lý như sau. Nguyên nhân của sự cố hiện đang trong quá trình rà soát chuyên sâu từ phía hệ thống quản trị chương trình.
-Zalopay đã phối hợp chặt chẽ với bộ phận chuyên trách chương trình ưu đãi để xác minh lại nguyên nhân cụ thể và đánh giá tổng thể quyền lợi cho trường hợp của bạn. Ngay khi kết thúc quá trình kiểm tra, Zalopay sẽ thông báo rõ ràng về phương án bù thưởng sao cho đảm bảo bạn nhận đầy đủ lợi ích theo đúng cam kết ban đầu của chương trình.
-Zalopay một lần nữa xin lỗi vì sự bất tiện này. Nếu cần hỗ trợ thêm, bạn vui lòng gửi yêu cầu mới tại Trung tâm hỗ trợ để Zalopay phản hồi đến bạn nhanh chóng nhất.
-Cảm ơn bạn đã tin tưởng và sử dụng dịch vụ của Zalopay.</t>
-  </si>
-  <si>
-    <t>ISSUE-40959</t>
-  </si>
-  <si>
-    <t>Lending_paylater</t>
-  </si>
-  <si>
-    <t>Chào bạn,
-Cảm ơn bạn đã quan tâm và sử dụng dịch vụ của ứng dụng thanh toán Zalopay.
-Về thắc mắc liên quan đến quy tắc tính dư nợ theo kỳ và phân biệt giao dịch trên dịch vụ trả sau của Zalopay, Zalopay xin thông tin cụ thể như sau. Dư nợ được tính toán dựa trên từng kỳ thanh toán riêng biệt. Các giao dịch thuộc kỳ cũ đã được thanh toán xong sẽ không ảnh hưởng đến dư nợ hiện tại. Chỉ những giao dịch mới phát sinh trong kỳ đang tính toán mới được cộng vào tổng số tiền cần đóng.
-Để xem chi tiết, bạn có thể kiểm tra hóa đơn tại mục trả sau trên ứng dụng Zalopay. Tại đây, danh sách giao dịch sẽ được hiển thị rõ ràng theo từng kỳ hạn. Để Zalopay có thể hỗ trợ tra cứu chính xác dữ liệu giao dịch cá nhân, bạn vui lòng cung cấp số điện thoại đăng ký Zalopay.
-Nếu cần hỗ trợ thêm thông tin khác, bạn vui lòng gửi yêu cầu mới tại Trung tâm hỗ trợ để Zalopay phản hồi đến bạn nhanh chóng nhất.
-Cảm ơn bạn đã quan tâm và sử dụng dịch vụ của Zalopay.</t>
-  </si>
-  <si>
-    <t>ISSUE-40957</t>
-  </si>
-  <si>
-    <t>Account_Login/Register</t>
-  </si>
-  <si>
-    <t>Team Tài khoản &amp; An toàn bảo mật</t>
-  </si>
-  <si>
-    <t>Chào bạn,
-Zalopay xin lỗi vì đã để bạn có những trải nghiệm không tốt khi sử dụng dịch vụ.
-Zalopay đã tiếp nhận yêu cầu về việc xác minh thông tin tài khoản và đặt lại giới hạn mã OTP ngoại lệ của bạn. Hiểu rằng đây là tình huống khẩn cấp cần được hỗ trợ ngay lập tức, Zalopay đã tiến hành kiểm tra và chuyển yêu cầu của bạn đến bộ phận An toàn bảo mật để xem xét đặc biệt.
-Do quy trình an toàn nghiêm ngặt nhằm bảo vệ quyền lợi của bạn, việc điều chỉnh giới hạn OTP cần thời gian thẩm định từ hệ thống chuyên sâu. Hiện tại, Zalopay đang ưu tiên giải quyết yêu cầu này trong thời gian sớm nhất. Bạn vui lòng theo dõi thông báo kết quả qua ứng dụng hoặc số điện thoại đăng ký.
-Zalopay một lần nữa xin lỗi vì sự bất tiện này. Nếu cần hỗ trợ thêm, bạn vui lòng gửi yêu cầu mới tại Trung tâm hỗ trợ để Zalopay phản hồi đến bạn nhanh chóng nhất.
-Cảm ơn bạn đã tin tưởng và sử dụng dịch vụ của Zalopay.</t>
-  </si>
-  <si>
-    <t>Chào bạn,
-Cảm ơn bạn đã quan tâm và sử dụng dịch vụ của ứng dụng thanh toán Zalopay.
-Về thắc mắc của bạn liên quan đến quy trình xác minh danh tính khi thay đổi thông tin tài khoản, Zalopay xin cung cấp các lưu ý sau để quá trình thực hiện diễn ra thuận lợi:
-Đầu tiên, hãy kiểm tra quyền truy cập chức năng chụp hình cho ứng dụng Zalopay trên thiết bị của bạn. Bạn vào Cài đặt của điện thoại, chọn Quản lý ứng dụng, tìm ứng dụng Zalopay và đảm bảo quyền truy cập chức năng chụp hình được bật lên.
-Tiếp theo, khi chụp ảnh thẻ căn cước công dân, bạn cần lưu ý ánh sáng đủ rõ ràng, tránh tình trạng ngược sáng hoặc có bóng đổ che khuất thông tin trên thẻ. Nên đặt thẻ trên nền phẳng màu tối, không có vân rối để hệ thống dễ dàng quét thông tin chính xác.
-Hình ảnh cần bao trọn bốn góc của thẻ, nội dung chữ trên thẻ hiển thị rõ nét, không bị nhòe hay méo mó. Hãy giữ điện thoại ổn định trong lúc chụp để đảm bảo chất lượng hình ảnh tốt nhất.
-Nếu bạn đã thử lại mà vẫn chưa thành công, bạn vui lòng thử lại vào khung giờ hành chính hoặc kiểm tra kết nối mạng trước khi thao tác.
-Nếu cần hỗ trợ thêm thông tin khác, bạn vui lòng gửi yêu cầu mới tại Trung tâm hỗ trợ để Zalopay phản hồi đến bạn nhanh chóng nhất.
-Cảm ơn bạn đã quan tâm và sử dụng dịch vụ của Zalopay.</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -152,25 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -495,138 +396,286 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G10"/>
   <cols>
-    <col min="1" max="1" width="16.875" customWidth="1"/>
-    <col min="2" max="2" width="22.875" customWidth="1"/>
-    <col min="3" max="3" width="28.875" customWidth="1"/>
-    <col min="4" max="4" width="11.875" customWidth="1"/>
-    <col min="5" max="5" width="22.875" customWidth="1"/>
-    <col min="6" max="6" width="80.875" customWidth="1"/>
-    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="80.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="362.25" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="252" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Issue Key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Loại vấn đề</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Root Cause</v>
+      </c>
+      <c r="D1" t="str">
+        <v>SLA Status</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Escalate đến</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Phản hồi ZaloPay</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Trạng thái</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>ISSUE-41046</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Lending_paylater</v>
+      </c>
+      <c r="C2" t="str">
+        <v>External Factors</v>
+      </c>
+      <c r="D2" t="str">
+        <v>OK</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Chào bạn,
+Zalopay xin lỗi vì đã để bạn có những trải nghiệm không tốt khi sử dụng dịch vụ.
+Zalopay đã kiểm tra và xác nhận rằng đối tác TikTok Shop đã hoàn tiền về tài khoản. Tuy nhiên, việc cập nhật trạng thái giao dịch trên ứng dụng đôi khi cần một khoảng thời gian để đồng bộ giữa các hệ thống. Bạn vui lòng kiên nhẫn chờ hệ thống tự động cập nhật trạng thái mới nhất.
+Trong trường hợp trạng thái chưa được cập nhật sau thời gian chờ, bạn có thể liên hệ trực tiếp với TikTok Shop để được hỗ trợ chi tiết hơn về giao dịch này.
+Trân trọng cảm ơn bạn đã tin tưởng và sử dụng dịch vụ của Zalopay.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>ISSUE-41042</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Payment_Telco</v>
+      </c>
+      <c r="C3" t="str">
+        <v>User misuderstanding</v>
+      </c>
+      <c r="D3" t="str">
+        <v>OK</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Chào bạn,
+Cảm ơn bạn đã quan tâm và sử dụng dịch vụ của ứng dụng thanh toán Zalopay.
+Về thắc mắc của bạn liên quan đến sản phẩm VTVgo Plus, Zalopay xin giải thích như sau: Tiêu đề sản phẩm thường thể hiện tên gọi chung của gói dịch vụ, trong khi phần mô tả chi tiết sẽ cung cấp đầy đủ thông tin về thời hạn sử dụng cụ thể (ví dụ: số ngày hoặc thời điểm hết hạn) đi kèm với mỗi giao dịch. Sự khác biệt này nhằm giúp bạn dễ dàng nhận diện tên gói và nắm rõ quyền lợi đi kèm.
+Zalopay đã kiểm tra và xác nhận thông tin hiển thị trên ứng dụng đều chính xác theo quy định của đối tác VTVgo. Bạn vui lòng kiểm tra lại phần mô tả chi tiết sau khi thực hiện giao dịch để nắm rõ thời hạn sử dụng.
+Nếu bạn cần thêm bất kỳ hỗ trợ nào khác, đội ngũ Zalopay luôn sẵn sàng phục vụ.
+Trân trọng cảm ơn bạn.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>ISSUE-41024</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Promotion campaign</v>
+      </c>
+      <c r="C4" t="str">
+        <v>User need more Information</v>
+      </c>
+      <c r="D4" t="str">
+        <v>OK</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Chào bạn,
+Cảm ơn bạn đã quan tâm và sử dụng dịch vụ của ứng dụng thanh toán Zalopay.
+Zalopay xin cung cấp thông tin chi tiết về chương trình khuyến mãi bạn đang quan tâm. Chương trình này chỉ áp dụng cho ứng dụng có mã appid 4058. Để đảm bảo bạn nhận được ưu đãi, bạn vui lòng kiểm tra lại ứng dụng đang sử dụng và xác nhận mã appid đã chính xác.
+Nếu bạn cần hỗ trợ thêm về các bước kiểm tra hoặc có bất kỳ thắc mắc nào khác, đội ngũ Zalopay luôn sẵn sàng đồng hành cùng bạn.
+Trân trọng cảm ơn bạn đã tin tưởng và sử dụng dịch vụ của Zalopay.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>ISSUE-41021</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Promotion campaign</v>
+      </c>
+      <c r="C5" t="str">
+        <v>User misuderstanding</v>
+      </c>
+      <c r="D5" t="str">
+        <v>OK</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Chào bạn,
+Cảm ơn bạn đã quan tâm và sử dụng dịch vụ của ứng dụng thanh toán Zalopay.
+Zalopay đã kiểm tra lại thông tin về chương trình khuyến mãi ZFS_260401_119 liên quan đến dịch vụ gửi tiết kiệm. Theo quy định của chương trình, để nhận được phần thưởng cashback, sau khi khoản gửi tiết kiệm đáo hạn, bạn cần duy trì số dư tiền gửi trong tài khoản theo đúng thời gian và điều kiện đã công bố trên ứng dụng. Nếu số tiền được rút ra hoặc chuyển đi ngay sau khi đáo hạn, phần thưởng sẽ không được kích hoạt.
+Bạn vui lòng kiểm tra lại số dư và thời gian giữ tiền trong ứng dụng để đảm bảo đủ điều kiện nhận thưởng. Nếu cần hỗ trợ thêm về các bước thực hiện, đội ngũ Zalopay luôn sẵn sàng đồng hành cùng bạn.
+Trân trọng cảm ơn bạn đã tin tưởng và sử dụng dịch vụ của Zalopay.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>ISSUE-41017</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Lending_paylater</v>
+      </c>
+      <c r="C6" t="str">
+        <v>External Factors</v>
+      </c>
+      <c r="D6" t="str">
+        <v>OK</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Chào bạn,
+Zalopay xin lỗi vì đã để bạn có những trải nghiệm không tốt khi sử dụng dịch vụ.
+Zalopay đã kiểm tra và xác nhận vấn đề liên quan đến trạng thái giao dịch trả chậm của bạn. Để hỗ trợ bạn tốt nhất, bạn vui lòng kiểm tra số dư xu và trạng thái nợ hiện tại trong mục 'Trả chậm' trên ứng dụng Zalopay. Nếu thông tin trên ứng dụng chưa hiển thị chính xác hoặc bạn cần Zalopay xác minh lại với đối tác cổng thanh toán TPE, bạn vui lòng cung cấp thêm mã giao dịch cụ thể.
+Zalopay sẽ tiến hành liên hệ với đối tác TPE để xác nhận lại trạng thái giao dịch và cập nhật thông tin chi tiết cho bạn sớm nhất.
+Cảm ơn bạn đã tin tưởng và sử dụng dịch vụ của Zalopay.</v>
+      </c>
+      <c r="G6" t="str">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>ISSUE-41009</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Lending_installment</v>
+      </c>
+      <c r="C7" t="str">
+        <v>External Factors</v>
+      </c>
+      <c r="D7" t="str">
+        <v>OK</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Team Đối tác</v>
+      </c>
+      <c r="F7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Chào bạn,
+Zalopay xin lỗi vì đã để bạn có những trải nghiệm không tốt khi sử dụng dịch vụ.
+Zalopay đã nhận được yêu cầu của bạn liên quan đến giao dịch trả góp với đối tác CIMB. Hiện tại, Zalopay đang phối hợp chặt chẽ với Team Đối tác để kiểm tra kỹ lưỡng thông tin đối soát và xác nhận trạng thái gạch nợ từ phía CIMB.
+Ngay khi có kết quả kiểm tra từ đối tác, Zalopay sẽ cập nhật lại thông tin và xử lý dứt điểm cho bạn trong thời gian sớm nhất. Bạn vui lòng đợi phản hồi tiếp theo từ Zalopay.
+Cảm ơn bạn đã kiên nhẫn và sử dụng dịch vụ của ứng dụng thanh toán Zalopay.</v>
+      </c>
+      <c r="G7" t="str">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>ISSUE-41008</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Payment_Telco</v>
+      </c>
+      <c r="C8" t="str">
+        <v>User misuderstanding</v>
+      </c>
+      <c r="D8" t="str">
+        <v>OK</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Chào bạn,
+Cảm ơn bạn đã quan tâm và sử dụng dịch vụ của ứng dụng thanh toán Zalopay.
+Zalopay đã kiểm tra và xác nhận giao dịch mua gói cước VTVgo của bạn đã được thực hiện thành công. Để bạn nắm rõ hơn về quyền lợi và thời hạn sử dụng, bạn vui lòng kiểm tra thông tin chi tiết trên ứng dụng VTVgo hoặc liên hệ trực tiếp với nhà cung cấp dịch vụ VTVgo để được hỗ trợ cụ thể về gói cước bạn đã đăng ký.
+Zalopay luôn sẵn sàng đồng hành và hỗ trợ bạn trong mọi nhu cầu thanh toán.
+Trân trọng cảm ơn bạn đã tin tưởng và sử dụng dịch vụ của Zalopay.</v>
+      </c>
+      <c r="G8" t="str">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>ISSUE-41005</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Lending_cashloan</v>
+      </c>
+      <c r="C9" t="str">
+        <v>External Factors</v>
+      </c>
+      <c r="D9" t="str">
+        <v>OK</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Team Đối tác</v>
+      </c>
+      <c r="F9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Chào bạn,
+Zalopay xin lỗi vì đã để bạn có những trải nghiệm không tốt khi sử dụng dịch vụ.
+Zalopay đã kiểm tra và xác nhận nguyên nhân do sự cố từ hệ thống đối tác TNEX. Hiện tại, Zalopay đang phối hợp chặt chẽ với Team Đối tác để xử lý sự cố này và sẽ cập nhật lại cho bạn ngay khi có kết quả.
+Trân trọng cảm ơn bạn đã kiên nhẫn và đồng hành cùng Zalopay.</v>
+      </c>
+      <c r="G9" t="str">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>ISSUE-41004</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Payment_OnlineMerchant</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D10" t="str">
+        <v>OK</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Team Tài khoản</v>
+      </c>
+      <c r="F10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Chào bạn,
+Zalopay xin lỗi vì đã để bạn có những trải nghiệm không tốt khi sử dụng dịch vụ.
+Zalopay đã ghi nhận yêu cầu của bạn về việc hủy dịch vụ tự động và đóng tài khoản. Hiện tại, Zalopay đã chuyển yêu cầu này đến Team Tài khoản để tiến hành xử lý thủ công cho bạn trong thời gian sớm nhất.
+Zalopay rất cảm ơn bạn đã kiên nhẫn và mong nhận được phản hồi từ bạn sau khi quá trình xử lý hoàn tất.</v>
+      </c>
+      <c r="G10" t="str">
+        <v>OK</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 A4:G5 A2:E2 G2 A3:E3 G3" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
   </ignoredErrors>
 </worksheet>
 </file>